--- a/inventory_app/exports/box_id_manual_template.xlsx
+++ b/inventory_app/exports/box_id_manual_template.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/intuitivecreations2705gmail.com/Downloads/REAL-ED-INVENTORY-main/inventory_app/exports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1CAF265-29C7-3245-B90B-75A950F0F85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{F96709F2-B00E-3E45-8303-3F6771565765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5580" yWindow="2380" windowWidth="27640" windowHeight="16680" xr2:uid="{142F62EA-D1D4-F046-B623-10C064580D21}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{142F62EA-D1D4-F046-B623-10C064580D21}"/>
   </bookViews>
   <sheets>
     <sheet name="box_id_manual_template" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateCount="1"/>
+  <calcPr calcId="191029" iterateCount="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="290">
   <si>
     <t>box_key</t>
   </si>
@@ -34,21 +47,12 @@
     <t>box_label</t>
   </si>
   <si>
-    <t>box_type</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
     <t>AV1</t>
   </si>
   <si>
     <t>AV 1</t>
   </si>
   <si>
-    <t>Active</t>
-  </si>
-  <si>
     <t>AV10</t>
   </si>
   <si>
@@ -142,39 +146,6 @@
     <t>F2</t>
   </si>
   <si>
-    <t>FAC1</t>
-  </si>
-  <si>
-    <t>FAC 1</t>
-  </si>
-  <si>
-    <t>K1</t>
-  </si>
-  <si>
-    <t>K2</t>
-  </si>
-  <si>
-    <t>K3</t>
-  </si>
-  <si>
-    <t>KITCHEN</t>
-  </si>
-  <si>
-    <t>LEADERSHIPBOX</t>
-  </si>
-  <si>
-    <t>LEADERSHIP BOX</t>
-  </si>
-  <si>
-    <t>LHSHELVES</t>
-  </si>
-  <si>
-    <t>LH SHELVES</t>
-  </si>
-  <si>
-    <t>LOOSE</t>
-  </si>
-  <si>
     <t>MT10</t>
   </si>
   <si>
@@ -361,9 +332,6 @@
     <t>R9</t>
   </si>
   <si>
-    <t>R?</t>
-  </si>
-  <si>
     <t>SWEAT</t>
   </si>
   <si>
@@ -572,13 +540,387 @@
   </si>
   <si>
     <t>Z9</t>
+  </si>
+  <si>
+    <t>Music Desk Coverings</t>
+  </si>
+  <si>
+    <t>Dimmer Equipment</t>
+  </si>
+  <si>
+    <t>Audio Setup</t>
+  </si>
+  <si>
+    <t>Visuals Setup</t>
+  </si>
+  <si>
+    <t>TV in BOX</t>
+  </si>
+  <si>
+    <t>Speaker</t>
+  </si>
+  <si>
+    <t>Microphone Box</t>
+  </si>
+  <si>
+    <t>Manufacturer's  BOX</t>
+  </si>
+  <si>
+    <t>Miscelaneous Cables</t>
+  </si>
+  <si>
+    <t>AV11</t>
+  </si>
+  <si>
+    <t>AV12</t>
+  </si>
+  <si>
+    <t>Music Computer</t>
+  </si>
+  <si>
+    <t>Flood Lights</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Extra Cables - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos Display"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>SEMINARS ONLY</t>
+    </r>
+  </si>
+  <si>
+    <t>AV14</t>
+  </si>
+  <si>
+    <t>Main Monitor</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>AV18</t>
+  </si>
+  <si>
+    <t>AV19</t>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>F4</t>
+  </si>
+  <si>
+    <t>F5</t>
+  </si>
+  <si>
+    <t>Black Plastic Crate 01</t>
+  </si>
+  <si>
+    <t>Black Plastic Crate 02</t>
+  </si>
+  <si>
+    <t>20 ltr Drun Opaque</t>
+  </si>
+  <si>
+    <t>25 Ltr Drum Opaque</t>
+  </si>
+  <si>
+    <t>F6</t>
+  </si>
+  <si>
+    <t>F7</t>
+  </si>
+  <si>
+    <t>F8</t>
+  </si>
+  <si>
+    <t>F9</t>
+  </si>
+  <si>
+    <t>F10</t>
+  </si>
+  <si>
+    <t>F11</t>
+  </si>
+  <si>
+    <t>F12</t>
+  </si>
+  <si>
+    <t>F13</t>
+  </si>
+  <si>
+    <t>F14</t>
+  </si>
+  <si>
+    <t>F15</t>
+  </si>
+  <si>
+    <t>F16</t>
+  </si>
+  <si>
+    <t>F17</t>
+  </si>
+  <si>
+    <t>F18</t>
+  </si>
+  <si>
+    <t>F19</t>
+  </si>
+  <si>
+    <t>F20</t>
+  </si>
+  <si>
+    <t>Blue Barrel</t>
+  </si>
+  <si>
+    <t>FIRE TEAM STORE</t>
+  </si>
+  <si>
+    <t>MT1</t>
+  </si>
+  <si>
+    <t>MT2</t>
+  </si>
+  <si>
+    <t>Murrays Prop Box</t>
+  </si>
+  <si>
+    <t>Assorted Leathers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assorted Glass Candle Holders </t>
+  </si>
+  <si>
+    <t>Black Curtains Box</t>
+  </si>
+  <si>
+    <t>ArchItypes Demo Box</t>
+  </si>
+  <si>
+    <t>Real Sequence Box</t>
+  </si>
+  <si>
+    <t>Facilitator's Ritual Props (Magic Box)</t>
+  </si>
+  <si>
+    <t>LED Lights</t>
+  </si>
+  <si>
+    <t>MT28</t>
+  </si>
+  <si>
+    <t>MT29</t>
+  </si>
+  <si>
+    <t>MT30</t>
+  </si>
+  <si>
+    <t>MT31</t>
+  </si>
+  <si>
+    <t>MT32</t>
+  </si>
+  <si>
+    <t>MT33</t>
+  </si>
+  <si>
+    <t>MT34</t>
+  </si>
+  <si>
+    <t>MT35</t>
+  </si>
+  <si>
+    <t>MT36</t>
+  </si>
+  <si>
+    <t>MT37</t>
+  </si>
+  <si>
+    <t>MT38</t>
+  </si>
+  <si>
+    <t>MT39</t>
+  </si>
+  <si>
+    <t>MT40</t>
+  </si>
+  <si>
+    <t>Candles</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>R28</t>
+  </si>
+  <si>
+    <t>R29</t>
+  </si>
+  <si>
+    <t>R30</t>
+  </si>
+  <si>
+    <t>R31</t>
+  </si>
+  <si>
+    <t>R32</t>
+  </si>
+  <si>
+    <t>R33</t>
+  </si>
+  <si>
+    <t>R34</t>
+  </si>
+  <si>
+    <t>R47</t>
+  </si>
+  <si>
+    <t>R48</t>
+  </si>
+  <si>
+    <t>R49</t>
+  </si>
+  <si>
+    <t>R50</t>
+  </si>
+  <si>
+    <t>Ritual Gear</t>
+  </si>
+  <si>
+    <t>Light &amp; Shadow</t>
+  </si>
+  <si>
+    <t>Musical Instruments</t>
+  </si>
+  <si>
+    <t>Queen/King Ritual Flares</t>
+  </si>
+  <si>
+    <t>Small Mirrors</t>
+  </si>
+  <si>
+    <t>Golden Ball Stands - Gold</t>
+  </si>
+  <si>
+    <t>Illuminated Golden Key Ball</t>
+  </si>
+  <si>
+    <t>Sorbolene Mixing Equipment</t>
+  </si>
+  <si>
+    <t>Mixed Sorbolene Container</t>
+  </si>
+  <si>
+    <t>Arrow Break Kits</t>
+  </si>
+  <si>
+    <t>Grove Nets</t>
+  </si>
+  <si>
+    <t>Knighting Mats</t>
+  </si>
+  <si>
+    <t>Tee Light Candle Holders</t>
+  </si>
+  <si>
+    <t>Big Crystal Ball</t>
+  </si>
+  <si>
+    <t>Purple Pedestal Cover</t>
+  </si>
+  <si>
+    <t>Med.Yellow Tub - Warm Sorbolene</t>
+  </si>
+  <si>
+    <t>Small Yellow Tub - For Warm Sorbolene</t>
+  </si>
+  <si>
+    <t>Towels</t>
+  </si>
+  <si>
+    <t>Assorted Black and White off cuts</t>
+  </si>
+  <si>
+    <t>Black Fitted Sheets</t>
+  </si>
+  <si>
+    <t>Medium mirrors</t>
+  </si>
+  <si>
+    <t>Black Velour Backdrop Curtain</t>
+  </si>
+  <si>
+    <t>OLD Props Assorted</t>
+  </si>
+  <si>
+    <t>White Blind Folds</t>
+  </si>
+  <si>
+    <t>White Sheets</t>
+  </si>
+  <si>
+    <t>Black Sheets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Ropes(Sweat) </t>
+  </si>
+  <si>
+    <t>Facilitation Large Black Curtain</t>
+  </si>
+  <si>
+    <t>Green Rechargeable Lanterns</t>
+  </si>
+  <si>
+    <t>Assorted Bedding</t>
+  </si>
+  <si>
+    <t>Plastic Draws 1</t>
+  </si>
+  <si>
+    <t>Plastic Draws 2</t>
+  </si>
+  <si>
+    <t>Plastic Draws 3</t>
+  </si>
+  <si>
+    <t>Plastic Draws 4</t>
+  </si>
+  <si>
+    <t>Plastic Draws 5</t>
+  </si>
+  <si>
+    <t>Zen Area 2 - White Shelves</t>
+  </si>
+  <si>
+    <t>LOOSE ITEMS</t>
+  </si>
+  <si>
+    <t>Brass Bowls &amp; Racks</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -709,6 +1051,41 @@
     <font>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Display"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Display"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1055,8 +1432,41 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1432,1746 +1842,2447 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCDECB9-E38D-7D4E-9D64-F1F5BC872D97}">
-  <dimension ref="A1:F157"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:D202"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="3" width="10.83203125" style="3"/>
+    <col min="4" max="4" width="21.83203125" style="15" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="3"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="C2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F2" t="s">
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="B16" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C16" s="4"/>
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="B17" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="C17" s="4"/>
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B18" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="7"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="7"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="7"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="B21" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D21" s="7"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B22" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="C22" s="4"/>
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B23" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="C23" s="4"/>
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="B24" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="C24" s="4"/>
+      <c r="D24" s="7"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B25" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="C25" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B26" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="D31" s="7"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D32" s="7"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D33" s="7"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D34" s="7"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D35" s="7"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D36" s="7"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D37" s="7"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D38" s="7"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D39" s="7"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D40" s="7"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D41" s="7"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D42" s="7"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="D43" s="7"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D44" s="7"/>
+    </row>
+    <row r="45" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="B54" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B55" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F20" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="C55" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B56" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F21" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="C56" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B57" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="B58" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B59" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="C59" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B60" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="C60" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B61" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F25" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="C61" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B62" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="C62" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B63" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F27" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="B64" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B65" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A66" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="B66" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A67" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B67" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F29" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+      <c r="C67" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A68" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B68" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="C68" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A69" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B69" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F31" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+      <c r="C69" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A70" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B70" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F32" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+      <c r="C70" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A71" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B71" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>55</v>
-      </c>
-      <c r="B34" t="s">
-        <v>55</v>
-      </c>
-      <c r="F34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>56</v>
-      </c>
-      <c r="B35" t="s">
-        <v>56</v>
-      </c>
-      <c r="F35" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>57</v>
-      </c>
-      <c r="B36" t="s">
-        <v>57</v>
-      </c>
-      <c r="F36" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>58</v>
-      </c>
-      <c r="B37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F37" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>59</v>
-      </c>
-      <c r="B38" t="s">
-        <v>59</v>
-      </c>
-      <c r="F38" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>60</v>
-      </c>
-      <c r="B39" t="s">
-        <v>60</v>
-      </c>
-      <c r="F39" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>61</v>
-      </c>
-      <c r="B40" t="s">
-        <v>61</v>
-      </c>
-      <c r="F40" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+      <c r="C71" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A72" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A73" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A74" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A75" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A76" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A77" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A78" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="D78" s="14" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A79" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D79" s="14" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A80" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D80" s="14" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A81" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D81" s="14" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A82" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D82" s="14" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A83" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="D83" s="14" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A84" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="D84" s="14" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A85" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B85" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F41" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+      <c r="C85" s="4"/>
+      <c r="D85" s="7"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A86" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B42" t="s">
-        <v>63</v>
-      </c>
-      <c r="F42" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+      <c r="B86" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B43" t="s">
-        <v>64</v>
-      </c>
-      <c r="F43" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="C86" s="4"/>
+      <c r="D86" s="7"/>
+    </row>
+    <row r="87" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A87" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B87" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F44" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+      <c r="C87" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A88" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D88" s="7"/>
+    </row>
+    <row r="89" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A89" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A90" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A91" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A92" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D93" s="7"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A94" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D94" s="7"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D95" s="7"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A96" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="D96" s="7"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A97" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D97" s="7"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A98" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="D98" s="7"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A99" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D99" s="7"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A100" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="D100" s="7"/>
+    </row>
+    <row r="101" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A101" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B101" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F45" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+      <c r="C101" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D101" s="14" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A102" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B102" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F46" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
+      <c r="C102" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D102" s="13" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A103" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B103" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F47" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
+      <c r="C103" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A104" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B104" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F48" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+      <c r="C104" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A105" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B105" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F49" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>71</v>
-      </c>
-      <c r="B50" t="s">
-        <v>71</v>
-      </c>
-      <c r="F50" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
+      <c r="C105" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D105" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A106" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B106" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F51" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
+      <c r="C106" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D106" s="7"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A107" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B107" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F52" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
+      <c r="C107" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D107" s="7"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A108" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B108" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F53" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
+      <c r="C108" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A109" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B109" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F54" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
+      <c r="C109" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D109" s="14" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A110" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B110" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F55" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
+      <c r="C110" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A111" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B111" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D111" s="14" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A112" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F56" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
+      <c r="B112" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A113" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B113" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F57" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>80</v>
-      </c>
-      <c r="B58" t="s">
-        <v>80</v>
-      </c>
-      <c r="F58" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
+      <c r="C113" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A114" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D114" s="7"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A115" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D115" s="7"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A116" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="D116" s="7"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A117" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D117" s="7"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A118" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D118" s="7"/>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A119" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D119" s="7"/>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A120" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="D120" s="7"/>
+    </row>
+    <row r="121" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A121" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B121" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F59" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
+      <c r="C121" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A122" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B122" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F60" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
+      <c r="C122" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A123" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B123" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F61" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
+      <c r="C123" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D123" s="7"/>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A124" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B124" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="F62" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
+      <c r="C124" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D124" s="7"/>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A125" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B125" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="F63" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>86</v>
-      </c>
-      <c r="B64" t="s">
-        <v>86</v>
-      </c>
-      <c r="F64" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
+      <c r="C125" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D125" s="7"/>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A126" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B126" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F65" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
+      <c r="C126" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D126" s="7"/>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A127" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B127" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="F66" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
+      <c r="C127" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D127" s="7"/>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A128" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B128" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="F67" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
+      <c r="C128" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D128" s="7"/>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A129" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B129" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F68" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
+      <c r="C129" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D129" s="7"/>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A130" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B130" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="F69" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
+      <c r="C130" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D130" s="7"/>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A131" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B131" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F70" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
+      <c r="C131" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D131" s="7"/>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A132" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B132" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F71" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>94</v>
-      </c>
-      <c r="B72" t="s">
-        <v>94</v>
-      </c>
-      <c r="F72" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>95</v>
-      </c>
-      <c r="B73" t="s">
-        <v>95</v>
-      </c>
-      <c r="F73" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>96</v>
-      </c>
-      <c r="B74" t="s">
-        <v>96</v>
-      </c>
-      <c r="F74" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>97</v>
-      </c>
-      <c r="B75" t="s">
-        <v>97</v>
-      </c>
-      <c r="F75" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>98</v>
-      </c>
-      <c r="B76" t="s">
-        <v>98</v>
-      </c>
-      <c r="F76" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
+      <c r="C132" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D132" s="7"/>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A133" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D133" s="7"/>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A134" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D134" s="7"/>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A135" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="D135" s="7"/>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A136" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D136" s="7"/>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A137" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B137" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F77" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
+      <c r="C137" s="4"/>
+      <c r="D137" s="7"/>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A138" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B78" t="s">
-        <v>100</v>
-      </c>
-      <c r="F78" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
+      <c r="B138" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B79" t="s">
-        <v>101</v>
-      </c>
-      <c r="F79" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
+      <c r="C138" s="4"/>
+      <c r="D138" s="7"/>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A139" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B139" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F80" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
+      <c r="C139" s="4"/>
+      <c r="D139" s="7"/>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A140" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B81" t="s">
-        <v>103</v>
-      </c>
-      <c r="F81" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
+      <c r="B140" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B82" t="s">
-        <v>104</v>
-      </c>
-      <c r="F82" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
+      <c r="C140" s="4"/>
+      <c r="D140" s="7"/>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A141" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B83" t="s">
-        <v>105</v>
-      </c>
-      <c r="F83" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
+      <c r="B141" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B84" t="s">
-        <v>106</v>
-      </c>
-      <c r="F84" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
+      <c r="C141" s="4"/>
+      <c r="D141" s="7"/>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A142" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B142" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="F85" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
+      <c r="C142" s="4"/>
+      <c r="D142" s="7"/>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A143" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B143" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="F86" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
+      <c r="C143" s="4"/>
+      <c r="D143" s="7"/>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A144" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B144" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="F87" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
+      <c r="C144" s="4"/>
+      <c r="D144" s="7"/>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A145" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B145" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="F88" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
+      <c r="C145" s="4"/>
+      <c r="D145" s="7"/>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A146" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B146" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="F89" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
+      <c r="C146" s="4"/>
+      <c r="D146" s="7"/>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A147" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B147" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="F90" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
+      <c r="C147" s="4"/>
+      <c r="D147" s="7"/>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A148" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B148" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="F91" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
+      <c r="C148" s="4"/>
+      <c r="D148" s="7"/>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A149" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B92" t="s">
-        <v>114</v>
-      </c>
-      <c r="F92" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
+      <c r="B149" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B93" t="s">
+      <c r="C149" s="4"/>
+      <c r="D149" s="7"/>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A150" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="F93" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
+      <c r="B150" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C150" s="4"/>
+      <c r="D150" s="7"/>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A151" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B151" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F94" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
+      <c r="C151" s="4"/>
+      <c r="D151" s="7"/>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A152" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B152" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C152" s="4"/>
+      <c r="D152" s="7"/>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A153" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F95" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
+      <c r="B153" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C153" s="4"/>
+      <c r="D153" s="7"/>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A154" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B154" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C154" s="4"/>
+      <c r="D154" s="7"/>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A155" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F96" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
+      <c r="B155" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C155" s="4"/>
+      <c r="D155" s="7"/>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A156" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B156" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="F97" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
+      <c r="C156" s="4"/>
+      <c r="D156" s="7"/>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A157" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B157" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="F98" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A99" t="s">
+      <c r="C157" s="4"/>
+      <c r="D157" s="7"/>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A158" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B158" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="F99" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A100" t="s">
+      <c r="C158" s="4"/>
+      <c r="D158" s="7"/>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A159" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B159" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="F100" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
+      <c r="C159" s="4"/>
+      <c r="D159" s="7"/>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A160" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B160" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="F101" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
+      <c r="C160" s="4"/>
+      <c r="D160" s="7"/>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A161" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B161" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="F102" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A103" t="s">
+      <c r="C161" s="4"/>
+      <c r="D161" s="7"/>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A162" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B162" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F103" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
+      <c r="C162" s="4"/>
+      <c r="D162" s="7"/>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A163" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B163" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C163" s="4"/>
+      <c r="D163" s="7"/>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A164" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F104" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
+      <c r="B164" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C164" s="4"/>
+      <c r="D164" s="7"/>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A165" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B165" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="F105" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A106" t="s">
+      <c r="C165" s="4"/>
+      <c r="D165" s="7"/>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A166" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B166" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F106" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A107" t="s">
+      <c r="C166" s="4"/>
+      <c r="D166" s="7"/>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A167" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B167" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F107" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A108" t="s">
+      <c r="C167" s="4"/>
+      <c r="D167" s="7"/>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A168" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B168" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="F108" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A109" t="s">
+      <c r="C168" s="4"/>
+      <c r="D168" s="7"/>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A169" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B169" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="F109" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
+      <c r="C169" s="4"/>
+      <c r="D169" s="7"/>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A170" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B170" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="F110" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A111" t="s">
+      <c r="C170" s="4"/>
+      <c r="D170" s="7"/>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A171" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B171" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="F111" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A112" t="s">
+      <c r="C171" s="4"/>
+      <c r="D171" s="7"/>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A172" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B172" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F112" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A113" t="s">
+      <c r="C172" s="4"/>
+      <c r="D172" s="7"/>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A173" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B173" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="F113" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
+      <c r="C173" s="4"/>
+      <c r="D173" s="7"/>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A174" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B174" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F114" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A115" t="s">
+      <c r="C174" s="4"/>
+      <c r="D174" s="7"/>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A175" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B175" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F115" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A116" t="s">
+      <c r="C175" s="4"/>
+      <c r="D175" s="7"/>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A176" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B176" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="F116" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A117" t="s">
+      <c r="C176" s="4"/>
+      <c r="D176" s="7"/>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A177" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B177" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="F117" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A118" t="s">
+      <c r="C177" s="4"/>
+      <c r="D177" s="7"/>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A178" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B178" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="F118" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A119" t="s">
+      <c r="C178" s="4"/>
+      <c r="D178" s="7"/>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A179" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B179" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="F119" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A120" t="s">
+      <c r="C179" s="4"/>
+      <c r="D179" s="7"/>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A180" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B180" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="F120" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A121" t="s">
+      <c r="C180" s="4"/>
+      <c r="D180" s="7"/>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A181" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B181" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="F121" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A122" t="s">
+      <c r="C181" s="4"/>
+      <c r="D181" s="7"/>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A182" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B182" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="F122" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A123" t="s">
+      <c r="C182" s="4"/>
+      <c r="D182" s="7"/>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A183" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B183" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="F123" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A124" t="s">
+      <c r="C183" s="4"/>
+      <c r="D183" s="7"/>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A184" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B184" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="F124" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A125" t="s">
+      <c r="C184" s="4"/>
+      <c r="D184" s="7"/>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A185" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B185" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="F125" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A126" t="s">
+      <c r="C185" s="4"/>
+      <c r="D185" s="7"/>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A186" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B186" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="F126" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A127" t="s">
+      <c r="C186" s="4"/>
+      <c r="D186" s="7"/>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A187" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B187" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F127" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A128" t="s">
+      <c r="C187" s="4"/>
+      <c r="D187" s="7"/>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A188" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B188" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="F128" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A129" t="s">
+      <c r="C188" s="4"/>
+      <c r="D188" s="7"/>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A189" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B189" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F129" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A130" t="s">
+      <c r="C189" s="4"/>
+      <c r="D189" s="7"/>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A190" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B190" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="F130" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A131" t="s">
+      <c r="C190" s="4"/>
+      <c r="D190" s="7"/>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A191" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B191" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="F131" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A132" t="s">
+      <c r="C191" s="4"/>
+      <c r="D191" s="7"/>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A192" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B192" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="F132" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A133" t="s">
+      <c r="C192" s="4"/>
+      <c r="D192" s="7"/>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A193" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B193" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="F133" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A134" t="s">
+      <c r="C193" s="4"/>
+      <c r="D193" s="7"/>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A194" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B194" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="F134" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A135" t="s">
+      <c r="C194" s="4"/>
+      <c r="D194" s="7"/>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A195" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B195" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="F135" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A136" t="s">
+      <c r="C195" s="4"/>
+      <c r="D195" s="7"/>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A196" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B196" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="F136" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A137" t="s">
+      <c r="C196" s="4"/>
+      <c r="D196" s="7"/>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A197" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B197" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="F137" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A138" t="s">
+      <c r="C197" s="4"/>
+      <c r="D197" s="7"/>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A198" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B198" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F138" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A139" t="s">
+      <c r="C198" s="4"/>
+      <c r="D198" s="7"/>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A199" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B199" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="F139" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A140" t="s">
+      <c r="C199" s="4"/>
+      <c r="D199" s="7"/>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A200" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B200" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="F140" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A141" t="s">
+      <c r="C200" s="4"/>
+      <c r="D200" s="7"/>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A201" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B201" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="F141" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A142" t="s">
+      <c r="C201" s="4"/>
+      <c r="D201" s="7"/>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A202" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B202" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="F142" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A143" t="s">
-        <v>169</v>
-      </c>
-      <c r="B143" t="s">
-        <v>169</v>
-      </c>
-      <c r="F143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A144" t="s">
-        <v>170</v>
-      </c>
-      <c r="B144" t="s">
-        <v>170</v>
-      </c>
-      <c r="F144" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A145" t="s">
-        <v>171</v>
-      </c>
-      <c r="B145" t="s">
-        <v>171</v>
-      </c>
-      <c r="F145" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A146" t="s">
-        <v>172</v>
-      </c>
-      <c r="B146" t="s">
-        <v>172</v>
-      </c>
-      <c r="F146" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A147" t="s">
-        <v>173</v>
-      </c>
-      <c r="B147" t="s">
-        <v>173</v>
-      </c>
-      <c r="F147" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A148" t="s">
-        <v>174</v>
-      </c>
-      <c r="B148" t="s">
-        <v>174</v>
-      </c>
-      <c r="F148" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A149" t="s">
-        <v>175</v>
-      </c>
-      <c r="B149" t="s">
-        <v>175</v>
-      </c>
-      <c r="F149" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A150" t="s">
-        <v>176</v>
-      </c>
-      <c r="B150" t="s">
-        <v>176</v>
-      </c>
-      <c r="F150" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A151" t="s">
-        <v>177</v>
-      </c>
-      <c r="B151" t="s">
-        <v>177</v>
-      </c>
-      <c r="F151" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A152" t="s">
-        <v>178</v>
-      </c>
-      <c r="B152" t="s">
-        <v>178</v>
-      </c>
-      <c r="F152" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A153" t="s">
-        <v>179</v>
-      </c>
-      <c r="B153" t="s">
-        <v>179</v>
-      </c>
-      <c r="F153" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A154" t="s">
-        <v>180</v>
-      </c>
-      <c r="B154" t="s">
-        <v>180</v>
-      </c>
-      <c r="F154" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A155" t="s">
-        <v>181</v>
-      </c>
-      <c r="B155" t="s">
-        <v>181</v>
-      </c>
-      <c r="F155" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A156" t="s">
-        <v>182</v>
-      </c>
-      <c r="B156" t="s">
-        <v>182</v>
-      </c>
-      <c r="F156" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A157" t="s">
-        <v>183</v>
-      </c>
-      <c r="B157" t="s">
-        <v>183</v>
-      </c>
-      <c r="F157" t="s">
-        <v>8</v>
-      </c>
+      <c r="C202" s="4"/>
+      <c r="D202" s="7"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>